--- a/MathAn/timeAn/Data/pcb3.xlsx
+++ b/MathAn/timeAn/Data/pcb3.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20745" windowHeight="9675"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet r:id="rId1" sheetId="1" name="Sheet1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -1384,127 +1384,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1512,240 +1399,24 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1755,31 +1426,16 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1787,294 +1443,51 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+  </cellStyleXfs>
+  <cellXfs count="10">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-  </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2085,10 +1498,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -2126,69 +1539,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -2212,54 +1627,53 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
                 <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="15000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
+                <a:tint val="94000"/>
                 <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
+              <a:shade val="9500"/>
               <a:satMod val="105000"/>
             </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -2269,7 +1683,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -2278,7 +1692,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -2287,7 +1701,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -2295,10 +1709,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
+              <a:rot rev="0" lon="0" lat="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -2327,7 +1741,7 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
+                <a:tint val="20000"/>
                 <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
@@ -2340,13 +1754,12 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
                 <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
+                <a:tint val="80000"/>
                 <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
@@ -2359,33 +1772,37 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
   <dimension ref="A1:F158"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.25" customWidth="1"/>
-    <col min="2" max="2" width="10.375" customWidth="1"/>
-    <col min="3" max="3" width="12.875" customWidth="1"/>
-    <col min="4" max="4" width="7.375" customWidth="1"/>
-    <col min="5" max="6" width="18.25" customWidth="1"/>
+    <col min="1" max="1" style="7" width="18.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="10.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="8" width="12.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="9" width="7.433571428571429" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="7" width="18.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="7" width="18.290714285714284" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -2395,3151 +1812,3147 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="5">
         <v>71</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="5">
         <v>618</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="6">
         <v>10.25</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="5">
         <v>653</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="5">
         <v>23</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="6">
         <v>4.83</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="5">
         <v>702</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="5">
         <v>2</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="6">
         <v>9.72</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="5">
         <v>662</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="5">
         <v>30</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="6">
         <v>8.21</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="5">
         <v>607</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="5">
         <v>74</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="6">
         <v>6.05</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="s">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="5">
         <v>715</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="5">
         <v>0</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="6">
         <v>13.24</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="5">
         <v>703</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="5">
         <v>42</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="6">
         <v>4.6</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="5">
         <v>752</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="5">
         <v>21</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="6">
         <v>4.7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="5">
         <v>748</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="5">
         <v>29</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="6">
         <v>7.16</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
-      <c r="A11" t="s">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+      <c r="A11" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="5">
         <v>506</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="5">
         <v>251</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="6">
         <v>5.18</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
-      <c r="A12" t="s">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+      <c r="A12" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="5">
         <v>293</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="5">
         <v>434</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="6">
         <v>4.65</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
-      <c r="A13" t="s">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="A13" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="5">
         <v>799</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="5">
         <v>30</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="6">
         <v>4.87</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
-      <c r="A14" t="s">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+      <c r="A14" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="5">
         <v>517</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="5">
         <v>295</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="6">
         <v>4.67</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
-      <c r="A15" t="s">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+      <c r="A15" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="5">
         <v>371</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="5">
         <v>457</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="6">
         <v>5.18</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
-      <c r="A16" t="s">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+      <c r="A16" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="5">
         <v>804</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="5">
         <v>37</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="6">
         <v>5.94</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
-      <c r="A17" t="s">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+      <c r="A17" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="5">
         <v>890</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="5">
         <v>11</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="6">
         <v>4.05</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
-      <c r="A18" t="s">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+      <c r="A18" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="5">
         <v>728</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="5">
         <v>151</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="6">
         <v>8.8</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
-      <c r="A19" t="s">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+      <c r="A19" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="5">
         <v>908</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="5">
         <v>2</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="6">
         <v>7.97</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
-      <c r="A20" t="s">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+      <c r="A20" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="5">
         <v>220</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="5">
         <v>676</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="6">
         <v>4.14</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
-      <c r="A21" t="s">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+      <c r="A21" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="5">
         <v>838</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="5">
         <v>79</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="6">
         <v>6.73</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
-      <c r="A22" t="s">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+      <c r="A22" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="5">
         <v>619</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="5">
         <v>264</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="6">
         <v>4.01</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
-      <c r="A23" t="s">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+      <c r="A23" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="5">
         <v>821</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="5">
         <v>73</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="6">
         <v>4.76</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
-      <c r="A24" t="s">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+      <c r="A24" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="5">
         <v>931</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="5">
         <v>0</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="6">
         <v>10.06</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" s="4" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
-      <c r="A25" t="s">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+      <c r="A25" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="5">
         <v>886</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="5">
         <v>19</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="6">
         <v>5.11</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F25" s="4" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
-      <c r="A26" t="s">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+      <c r="A26" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="5">
         <v>766</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="5">
         <v>124</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="6">
         <v>4.53</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" s="4" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
-      <c r="A27" t="s">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+      <c r="A27" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="5">
         <v>655</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="5">
         <v>158</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="6">
         <v>4.17</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F27" s="4" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
-      <c r="A28" t="s">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+      <c r="A28" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="5">
         <v>583</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="5">
         <v>225</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="6">
         <v>4.05</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F28" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
-      <c r="A29" t="s">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+      <c r="A29" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="5">
         <v>704</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="5">
         <v>63</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="6">
         <v>8.08</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F29" s="4" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
-      <c r="A30" t="s">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+      <c r="A30" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="5">
         <v>730</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="5">
         <v>39</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="6">
         <v>7.66</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F30" s="4" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
-      <c r="A31" t="s">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+      <c r="A31" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="5">
         <v>506</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="5">
         <v>239</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="6">
         <v>4.14</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F31" s="4" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
-      <c r="A32" t="s">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+      <c r="A32" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="5">
         <v>138</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="5">
         <v>689</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="6">
         <v>4.17</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F32" s="4" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
-      <c r="A33" t="s">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+      <c r="A33" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="5">
         <v>455</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="5">
         <v>346</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="6">
         <v>4.94</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E33" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F33" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
-      <c r="A34" t="s">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
+      <c r="A34" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="5">
         <v>690</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="5">
         <v>129</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="6">
         <v>5.24</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E34" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F34" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
-      <c r="A35" t="s">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
+      <c r="A35" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="5">
         <v>386</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="5">
         <v>423</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="6">
         <v>6.2</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F35" s="4" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
-      <c r="A36" t="s">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
+      <c r="A36" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="5">
         <v>383</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="5">
         <v>429</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="6">
         <v>5.12</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F36" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
-      <c r="A37" t="s">
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
+      <c r="A37" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="5">
         <v>508</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="5">
         <v>288</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="6">
         <v>8.22</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F37" s="4" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
-      <c r="A38" t="s">
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
+      <c r="A38" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="5">
         <v>737</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="5">
         <v>96</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="6">
         <v>6.98</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E38" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="F38" t="s">
+      <c r="F38" s="4" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
-      <c r="A39" t="s">
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
+      <c r="A39" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="5">
         <v>304</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="5">
         <v>538</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="6">
         <v>4.15</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E39" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F39" s="4" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
-      <c r="A40" t="s">
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
+      <c r="A40" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="5">
         <v>370</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="5">
         <v>466</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="6">
         <v>6.97</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F40" s="4" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
-      <c r="A41" t="s">
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
+      <c r="A41" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="B41">
+      <c r="B41" s="5">
         <v>669</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="5">
         <v>169</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="6">
         <v>4.79</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E41" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F41" s="4" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
-      <c r="A42" t="s">
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
+      <c r="A42" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="5">
         <v>821</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="5">
         <v>29</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="6">
         <v>6.62</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E42" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="F42" t="s">
+      <c r="F42" s="4" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
-      <c r="A43" t="s">
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
+      <c r="A43" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="B43">
+      <c r="B43" s="5">
         <v>728</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="5">
         <v>129</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="6">
         <v>4.66</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E43" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="F43" t="s">
+      <c r="F43" s="4" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
-      <c r="A44" t="s">
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
+      <c r="A44" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="5">
         <v>739</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="5">
         <v>102</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="6">
         <v>5.12</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E44" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F44" t="s">
+      <c r="F44" s="4" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
-      <c r="A45" t="s">
+    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
+      <c r="A45" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B45">
+      <c r="B45" s="5">
         <v>673</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="5">
         <v>171</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="6">
         <v>4.33</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E45" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="F45" t="s">
+      <c r="F45" s="4" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
-      <c r="A46" t="s">
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
+      <c r="A46" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="B46">
+      <c r="B46" s="5">
         <v>466</v>
       </c>
-      <c r="C46">
+      <c r="C46" s="5">
         <v>384</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="6">
         <v>5.16</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E46" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="F46" t="s">
+      <c r="F46" s="4" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
-      <c r="A47" t="s">
+    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
+      <c r="A47" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="B47">
+      <c r="B47" s="5">
         <v>428</v>
       </c>
-      <c r="C47">
+      <c r="C47" s="5">
         <v>413</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="6">
         <v>7.87</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E47" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="F47" t="s">
+      <c r="F47" s="4" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
-      <c r="A48" t="s">
+    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
+      <c r="A48" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="B48">
+      <c r="B48" s="5">
         <v>369</v>
       </c>
-      <c r="C48">
+      <c r="C48" s="5">
         <v>479</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="6">
         <v>6.73</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E48" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F48" s="4" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
-      <c r="A49" t="s">
+    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
+      <c r="A49" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="B49">
+      <c r="B49" s="5">
         <v>556</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="5">
         <v>279</v>
       </c>
-      <c r="D49">
+      <c r="D49" s="6">
         <v>4.43</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E49" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="F49" t="s">
+      <c r="F49" s="4" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
-      <c r="A50" t="s">
+    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
+      <c r="A50" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B50">
+      <c r="B50" s="5">
         <v>798</v>
       </c>
-      <c r="C50">
+      <c r="C50" s="5">
         <v>61</v>
       </c>
-      <c r="D50">
+      <c r="D50" s="5">
         <v>6</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E50" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="F50" t="s">
+      <c r="F50" s="4" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
-      <c r="A51" t="s">
+    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
+      <c r="A51" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="B51">
+      <c r="B51" s="5">
         <v>752</v>
       </c>
-      <c r="C51">
+      <c r="C51" s="5">
         <v>97</v>
       </c>
-      <c r="D51">
+      <c r="D51" s="6">
         <v>6.73</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E51" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="F51" t="s">
+      <c r="F51" s="4" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
-      <c r="A52" t="s">
+    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
+      <c r="A52" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B52">
+      <c r="B52" s="5">
         <v>167</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="5">
         <v>695</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="6">
         <v>6.56</v>
       </c>
-      <c r="E52" t="s">
+      <c r="E52" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="F52" t="s">
+      <c r="F52" s="4" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
-      <c r="A53" t="s">
+    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
+      <c r="A53" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="B53">
+      <c r="B53" s="5">
         <v>333</v>
       </c>
-      <c r="C53">
+      <c r="C53" s="5">
         <v>517</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="6">
         <v>7.6</v>
       </c>
-      <c r="E53" t="s">
+      <c r="E53" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F53" t="s">
+      <c r="F53" s="4" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
-      <c r="A54" t="s">
+    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
+      <c r="A54" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="B54">
+      <c r="B54" s="5">
         <v>628</v>
       </c>
-      <c r="C54">
+      <c r="C54" s="5">
         <v>221</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="6">
         <v>7.62</v>
       </c>
-      <c r="E54" t="s">
+      <c r="E54" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="F54" t="s">
+      <c r="F54" s="4" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
-      <c r="A55" t="s">
+    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
+      <c r="A55" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="B55">
+      <c r="B55" s="5">
         <v>557</v>
       </c>
-      <c r="C55">
+      <c r="C55" s="5">
         <v>277</v>
       </c>
-      <c r="D55">
+      <c r="D55" s="6">
         <v>6.95</v>
       </c>
-      <c r="E55" t="s">
+      <c r="E55" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="F55" t="s">
+      <c r="F55" s="4" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
-      <c r="A56" t="s">
+    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
+      <c r="A56" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="B56">
+      <c r="B56" s="5">
         <v>702</v>
       </c>
-      <c r="C56">
+      <c r="C56" s="5">
         <v>134</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="6">
         <v>4.14</v>
       </c>
-      <c r="E56" t="s">
+      <c r="E56" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="F56" t="s">
+      <c r="F56" s="4" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
-      <c r="A57" t="s">
+    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
+      <c r="A57" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="B57">
+      <c r="B57" s="5">
         <v>710</v>
       </c>
-      <c r="C57">
+      <c r="C57" s="5">
         <v>119</v>
       </c>
-      <c r="D57">
+      <c r="D57" s="6">
         <v>4.81</v>
       </c>
-      <c r="E57" t="s">
+      <c r="E57" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="F57" t="s">
+      <c r="F57" s="4" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
-      <c r="A58" t="s">
+    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
+      <c r="A58" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="B58">
+      <c r="B58" s="5">
         <v>332</v>
       </c>
-      <c r="C58">
+      <c r="C58" s="5">
         <v>506</v>
       </c>
-      <c r="D58">
+      <c r="D58" s="6">
         <v>6.64</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E58" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="F58" t="s">
+      <c r="F58" s="4" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
-      <c r="A59" t="s">
+    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
+      <c r="A59" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="B59">
+      <c r="B59" s="5">
         <v>391</v>
       </c>
-      <c r="C59">
+      <c r="C59" s="5">
         <v>446</v>
       </c>
-      <c r="D59">
+      <c r="D59" s="6">
         <v>4.48</v>
       </c>
-      <c r="E59" t="s">
+      <c r="E59" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="F59" t="s">
+      <c r="F59" s="4" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
-      <c r="A60" t="s">
+    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
+      <c r="A60" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="B60">
+      <c r="B60" s="5">
         <v>787</v>
       </c>
-      <c r="C60">
+      <c r="C60" s="5">
         <v>55</v>
       </c>
-      <c r="D60">
+      <c r="D60" s="6">
         <v>6.53</v>
       </c>
-      <c r="E60" t="s">
+      <c r="E60" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="F60" t="s">
+      <c r="F60" s="4" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="61" spans="1:6">
-      <c r="A61" t="s">
+    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
+      <c r="A61" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="B61">
+      <c r="B61" s="5">
         <v>698</v>
       </c>
-      <c r="C61">
+      <c r="C61" s="5">
         <v>123</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="6">
         <v>5.92</v>
       </c>
-      <c r="E61" t="s">
+      <c r="E61" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="F61" t="s">
+      <c r="F61" s="4" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="62" spans="1:6">
-      <c r="A62" t="s">
+    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
+      <c r="A62" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="B62">
+      <c r="B62" s="5">
         <v>413</v>
       </c>
-      <c r="C62">
+      <c r="C62" s="5">
         <v>428</v>
       </c>
-      <c r="D62">
+      <c r="D62" s="6">
         <v>4.43</v>
       </c>
-      <c r="E62" t="s">
+      <c r="E62" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="F62" t="s">
+      <c r="F62" s="4" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="63" spans="1:6">
-      <c r="A63" t="s">
+    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
+      <c r="A63" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="B63">
+      <c r="B63" s="5">
         <v>858</v>
       </c>
-      <c r="C63">
+      <c r="C63" s="5">
         <v>2</v>
       </c>
-      <c r="D63">
+      <c r="D63" s="6">
         <v>5.76</v>
       </c>
-      <c r="E63" t="s">
+      <c r="E63" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="F63" t="s">
+      <c r="F63" s="4" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="64" spans="1:6">
-      <c r="A64" t="s">
+    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
+      <c r="A64" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="B64">
+      <c r="B64" s="5">
         <v>859</v>
       </c>
-      <c r="C64">
+      <c r="C64" s="5">
         <v>1</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="6">
         <v>8.12</v>
       </c>
-      <c r="E64" t="s">
+      <c r="E64" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="F64" t="s">
+      <c r="F64" s="4" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
-      <c r="A65" t="s">
+    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
+      <c r="A65" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="B65">
+      <c r="B65" s="5">
         <v>853</v>
       </c>
-      <c r="C65">
+      <c r="C65" s="5">
         <v>1</v>
       </c>
-      <c r="D65">
+      <c r="D65" s="6">
         <v>14.95</v>
       </c>
-      <c r="E65" t="s">
+      <c r="E65" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="F65" t="s">
+      <c r="F65" s="4" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
-      <c r="A66" t="s">
+    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
+      <c r="A66" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="B66">
+      <c r="B66" s="5">
         <v>818</v>
       </c>
-      <c r="C66">
+      <c r="C66" s="5">
         <v>43</v>
       </c>
-      <c r="D66">
+      <c r="D66" s="6">
         <v>8.24</v>
       </c>
-      <c r="E66" t="s">
+      <c r="E66" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="F66" t="s">
+      <c r="F66" s="4" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
-      <c r="A67" t="s">
+    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
+      <c r="A67" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="B67">
+      <c r="B67" s="5">
         <v>604</v>
       </c>
-      <c r="C67">
+      <c r="C67" s="5">
         <v>223</v>
       </c>
-      <c r="D67">
+      <c r="D67" s="6">
         <v>5.12</v>
       </c>
-      <c r="E67" t="s">
+      <c r="E67" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="F67" t="s">
+      <c r="F67" s="4" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
-      <c r="A68" t="s">
+    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
+      <c r="A68" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="B68">
+      <c r="B68" s="5">
         <v>828</v>
       </c>
-      <c r="C68">
+      <c r="C68" s="5">
         <v>59</v>
       </c>
-      <c r="D68">
+      <c r="D68" s="6">
         <v>9.39</v>
       </c>
-      <c r="E68" t="s">
+      <c r="E68" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="F68" t="s">
+      <c r="F68" s="4" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
-      <c r="A69" t="s">
+    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
+      <c r="A69" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="B69">
+      <c r="B69" s="5">
         <v>460</v>
       </c>
-      <c r="C69">
+      <c r="C69" s="5">
         <v>394</v>
       </c>
-      <c r="D69">
+      <c r="D69" s="6">
         <v>6.01</v>
       </c>
-      <c r="E69" t="s">
+      <c r="E69" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="F69" t="s">
+      <c r="F69" s="4" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="70" spans="1:6">
-      <c r="A70" t="s">
+    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
+      <c r="A70" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="B70">
+      <c r="B70" s="5">
         <v>139</v>
       </c>
-      <c r="C70">
+      <c r="C70" s="5">
         <v>742</v>
       </c>
-      <c r="D70">
+      <c r="D70" s="6">
         <v>4.82</v>
       </c>
-      <c r="E70" t="s">
+      <c r="E70" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="F70" t="s">
+      <c r="F70" s="4" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
-      <c r="A71" t="s">
+    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
+      <c r="A71" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="B71">
+      <c r="B71" s="5">
         <v>887</v>
       </c>
-      <c r="C71">
+      <c r="C71" s="5">
         <v>0</v>
       </c>
-      <c r="D71">
+      <c r="D71" s="6">
         <v>4.45</v>
       </c>
-      <c r="E71" t="s">
+      <c r="E71" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="F71" t="s">
+      <c r="F71" s="4" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
-      <c r="A72" t="s">
+    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
+      <c r="A72" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="B72">
+      <c r="B72" s="5">
         <v>64</v>
       </c>
-      <c r="C72">
+      <c r="C72" s="5">
         <v>828</v>
       </c>
-      <c r="D72">
+      <c r="D72" s="6">
         <v>16.12</v>
       </c>
-      <c r="E72" t="s">
+      <c r="E72" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="F72" t="s">
+      <c r="F72" s="4" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
-      <c r="A73" t="s">
+    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
+      <c r="A73" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="B73">
+      <c r="B73" s="5">
         <v>309</v>
       </c>
-      <c r="C73">
+      <c r="C73" s="5">
         <v>604</v>
       </c>
-      <c r="D73">
+      <c r="D73" s="6">
         <v>7.33</v>
       </c>
-      <c r="E73" t="s">
+      <c r="E73" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="F73" t="s">
+      <c r="F73" s="4" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
-      <c r="A74" t="s">
+    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
+      <c r="A74" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="B74">
+      <c r="B74" s="5">
         <v>885</v>
       </c>
-      <c r="C74">
+      <c r="C74" s="5">
         <v>37</v>
       </c>
-      <c r="D74">
+      <c r="D74" s="6">
         <v>9.22</v>
       </c>
-      <c r="E74" t="s">
+      <c r="E74" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="F74" t="s">
+      <c r="F74" s="4" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
-      <c r="A75" t="s">
+    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
+      <c r="A75" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="B75">
+      <c r="B75" s="5">
         <v>822</v>
       </c>
-      <c r="C75">
+      <c r="C75" s="5">
         <v>89</v>
       </c>
-      <c r="D75">
+      <c r="D75" s="6">
         <v>6.83</v>
       </c>
-      <c r="E75" t="s">
+      <c r="E75" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="F75" t="s">
+      <c r="F75" s="4" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
-      <c r="A76" t="s">
+    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
+      <c r="A76" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="B76">
+      <c r="B76" s="5">
         <v>879</v>
       </c>
-      <c r="C76">
+      <c r="C76" s="5">
         <v>12</v>
       </c>
-      <c r="D76">
+      <c r="D76" s="6">
         <v>5.69</v>
       </c>
-      <c r="E76" t="s">
+      <c r="E76" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="F76" t="s">
+      <c r="F76" s="4" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
-      <c r="A77" t="s">
+    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
+      <c r="A77" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="B77">
+      <c r="B77" s="5">
         <v>540</v>
       </c>
-      <c r="C77">
+      <c r="C77" s="5">
         <v>292</v>
       </c>
-      <c r="D77">
+      <c r="D77" s="6">
         <v>4.89</v>
       </c>
-      <c r="E77" t="s">
+      <c r="E77" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="F77" t="s">
+      <c r="F77" s="4" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="78" spans="1:6">
-      <c r="A78" t="s">
+    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
+      <c r="A78" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="B78">
+      <c r="B78" s="5">
         <v>778</v>
       </c>
-      <c r="C78">
+      <c r="C78" s="5">
         <v>98</v>
       </c>
-      <c r="D78">
+      <c r="D78" s="6">
         <v>5.88</v>
       </c>
-      <c r="E78" t="s">
+      <c r="E78" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="F78" t="s">
+      <c r="F78" s="4" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
-      <c r="A79" t="s">
+    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
+      <c r="A79" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="B79">
+      <c r="B79" s="5">
         <v>895</v>
       </c>
-      <c r="C79">
+      <c r="C79" s="5">
         <v>1</v>
       </c>
-      <c r="D79">
+      <c r="D79" s="6">
         <v>5.84</v>
       </c>
-      <c r="E79" t="s">
+      <c r="E79" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="F79" t="s">
+      <c r="F79" s="4" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
-      <c r="A80" t="s">
+    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
+      <c r="A80" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="B80">
+      <c r="B80" s="5">
         <v>711</v>
       </c>
-      <c r="C80">
+      <c r="C80" s="5">
         <v>162</v>
       </c>
-      <c r="D80">
+      <c r="D80" s="6">
         <v>7.97</v>
       </c>
-      <c r="E80" t="s">
+      <c r="E80" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="F80" t="s">
+      <c r="F80" s="4" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
-      <c r="A81" t="s">
+    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
+      <c r="A81" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="B81">
+      <c r="B81" s="5">
         <v>676</v>
       </c>
-      <c r="C81">
+      <c r="C81" s="5">
         <v>196</v>
       </c>
-      <c r="D81">
+      <c r="D81" s="6">
         <v>5.69</v>
       </c>
-      <c r="E81" t="s">
+      <c r="E81" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="F81" t="s">
+      <c r="F81" s="4" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
-      <c r="A82" t="s">
+    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
+      <c r="A82" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="B82">
+      <c r="B82" s="5">
         <v>880</v>
       </c>
-      <c r="C82">
+      <c r="C82" s="5">
         <v>16</v>
       </c>
-      <c r="D82">
+      <c r="D82" s="6">
         <v>4.34</v>
       </c>
-      <c r="E82" t="s">
+      <c r="E82" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="F82" t="s">
+      <c r="F82" s="4" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
-      <c r="A83" t="s">
+    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
+      <c r="A83" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="B83">
+      <c r="B83" s="5">
         <v>529</v>
       </c>
-      <c r="C83">
+      <c r="C83" s="5">
         <v>343</v>
       </c>
-      <c r="D83">
+      <c r="D83" s="6">
         <v>6.1</v>
       </c>
-      <c r="E83" t="s">
+      <c r="E83" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="F83" t="s">
+      <c r="F83" s="4" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
-      <c r="A84" t="s">
+    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
+      <c r="A84" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="B84">
+      <c r="B84" s="5">
         <v>850</v>
       </c>
-      <c r="C84">
+      <c r="C84" s="5">
         <v>42</v>
       </c>
-      <c r="D84">
+      <c r="D84" s="6">
         <v>5.22</v>
       </c>
-      <c r="E84" t="s">
+      <c r="E84" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="F84" t="s">
+      <c r="F84" s="4" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
-      <c r="A85" t="s">
+    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
+      <c r="A85" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="B85">
+      <c r="B85" s="5">
         <v>776</v>
       </c>
-      <c r="C85">
+      <c r="C85" s="5">
         <v>88</v>
       </c>
-      <c r="D85">
+      <c r="D85" s="6">
         <v>4.58</v>
       </c>
-      <c r="E85" t="s">
+      <c r="E85" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="F85" t="s">
+      <c r="F85" s="4" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
-      <c r="A86" t="s">
+    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
+      <c r="A86" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="B86">
+      <c r="B86" s="5">
         <v>632</v>
       </c>
-      <c r="C86">
+      <c r="C86" s="5">
         <v>222</v>
       </c>
-      <c r="D86">
+      <c r="D86" s="6">
         <v>7.08</v>
       </c>
-      <c r="E86" t="s">
+      <c r="E86" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="F86" t="s">
+      <c r="F86" s="4" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
-      <c r="A87" t="s">
+    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
+      <c r="A87" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="B87">
+      <c r="B87" s="5">
         <v>874</v>
       </c>
-      <c r="C87">
+      <c r="C87" s="5">
         <v>11</v>
       </c>
-      <c r="D87">
+      <c r="D87" s="6">
         <v>6.6</v>
       </c>
-      <c r="E87" t="s">
+      <c r="E87" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="F87" t="s">
+      <c r="F87" s="4" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="88" spans="1:6">
-      <c r="A88" t="s">
+    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
+      <c r="A88" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="B88">
+      <c r="B88" s="5">
         <v>666</v>
       </c>
-      <c r="C88">
+      <c r="C88" s="5">
         <v>194</v>
       </c>
-      <c r="D88">
+      <c r="D88" s="6">
         <v>4.64</v>
       </c>
-      <c r="E88" t="s">
+      <c r="E88" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="F88" t="s">
+      <c r="F88" s="4" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
-      <c r="A89" t="s">
+    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
+      <c r="A89" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="B89">
+      <c r="B89" s="5">
         <v>555</v>
       </c>
-      <c r="C89">
+      <c r="C89" s="5">
         <v>291</v>
       </c>
-      <c r="D89">
+      <c r="D89" s="6">
         <v>5.53</v>
       </c>
-      <c r="E89" t="s">
+      <c r="E89" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="F89" t="s">
+      <c r="F89" s="4" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
-      <c r="A90" t="s">
+    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
+      <c r="A90" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="B90">
+      <c r="B90" s="5">
         <v>526</v>
       </c>
-      <c r="C90">
+      <c r="C90" s="5">
         <v>335</v>
       </c>
-      <c r="D90">
+      <c r="D90" s="6">
         <v>4.36</v>
       </c>
-      <c r="E90" t="s">
+      <c r="E90" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="F90" t="s">
+      <c r="F90" s="4" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="91" spans="1:6">
-      <c r="A91" t="s">
+    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
+      <c r="A91" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="B91">
+      <c r="B91" s="5">
         <v>293</v>
       </c>
-      <c r="C91">
+      <c r="C91" s="5">
         <v>586</v>
       </c>
-      <c r="D91">
+      <c r="D91" s="6">
         <v>4.96</v>
       </c>
-      <c r="E91" t="s">
+      <c r="E91" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="F91" t="s">
+      <c r="F91" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
-      <c r="A92" t="s">
+    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
+      <c r="A92" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="B92">
+      <c r="B92" s="5">
         <v>721</v>
       </c>
-      <c r="C92">
+      <c r="C92" s="5">
         <v>158</v>
       </c>
-      <c r="D92">
+      <c r="D92" s="6">
         <v>6.01</v>
       </c>
-      <c r="E92" t="s">
+      <c r="E92" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="F92" t="s">
+      <c r="F92" s="4" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
-      <c r="A93" t="s">
+    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
+      <c r="A93" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="B93">
+      <c r="B93" s="5">
         <v>725</v>
       </c>
-      <c r="C93">
+      <c r="C93" s="5">
         <v>139</v>
       </c>
-      <c r="D93">
+      <c r="D93" s="6">
         <v>7.46</v>
       </c>
-      <c r="E93" t="s">
+      <c r="E93" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="F93" t="s">
+      <c r="F93" s="4" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="94" spans="1:6">
-      <c r="A94" t="s">
+    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
+      <c r="A94" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="B94">
+      <c r="B94" s="5">
         <v>890</v>
       </c>
-      <c r="C94">
+      <c r="C94" s="5">
         <v>0</v>
       </c>
-      <c r="D94">
+      <c r="D94" s="6">
         <v>6.64</v>
       </c>
-      <c r="E94" t="s">
+      <c r="E94" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="F94" t="s">
+      <c r="F94" s="4" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
-      <c r="A95" t="s">
+    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
+      <c r="A95" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="B95">
+      <c r="B95" s="5">
         <v>893</v>
       </c>
-      <c r="C95">
+      <c r="C95" s="5">
         <v>0</v>
       </c>
-      <c r="D95">
+      <c r="D95" s="6">
         <v>5.36</v>
       </c>
-      <c r="E95" t="s">
+      <c r="E95" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="F95" t="s">
+      <c r="F95" s="4" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="96" spans="1:6">
-      <c r="A96" t="s">
+    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
+      <c r="A96" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="B96">
+      <c r="B96" s="5">
         <v>809</v>
       </c>
-      <c r="C96">
+      <c r="C96" s="5">
         <v>77</v>
       </c>
-      <c r="D96">
+      <c r="D96" s="6">
         <v>5.64</v>
       </c>
-      <c r="E96" t="s">
+      <c r="E96" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="F96" t="s">
+      <c r="F96" s="4" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
-      <c r="A97" t="s">
+    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
+      <c r="A97" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="B97">
+      <c r="B97" s="5">
         <v>819</v>
       </c>
-      <c r="C97">
+      <c r="C97" s="5">
         <v>76</v>
       </c>
-      <c r="D97">
+      <c r="D97" s="6">
         <v>5.19</v>
       </c>
-      <c r="E97" t="s">
+      <c r="E97" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="F97" t="s">
+      <c r="F97" s="4" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="98" spans="1:6">
-      <c r="A98" t="s">
+    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75">
+      <c r="A98" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="B98">
+      <c r="B98" s="5">
         <v>687</v>
       </c>
-      <c r="C98">
+      <c r="C98" s="5">
         <v>189</v>
       </c>
-      <c r="D98">
+      <c r="D98" s="6">
         <v>5.6</v>
       </c>
-      <c r="E98" t="s">
+      <c r="E98" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="F98" t="s">
+      <c r="F98" s="4" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="99" spans="1:6">
-      <c r="A99" t="s">
+    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75">
+      <c r="A99" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="B99">
+      <c r="B99" s="5">
         <v>429</v>
       </c>
-      <c r="C99">
+      <c r="C99" s="5">
         <v>436</v>
       </c>
-      <c r="D99">
+      <c r="D99" s="6">
         <v>4.58</v>
       </c>
-      <c r="E99" t="s">
+      <c r="E99" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="F99" t="s">
+      <c r="F99" s="4" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="100" spans="1:6">
-      <c r="A100" t="s">
+    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75">
+      <c r="A100" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="B100">
+      <c r="B100" s="5">
         <v>867</v>
       </c>
-      <c r="C100">
+      <c r="C100" s="5">
         <v>41</v>
       </c>
-      <c r="D100">
+      <c r="D100" s="6">
         <v>4.88</v>
       </c>
-      <c r="E100" t="s">
+      <c r="E100" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="F100" t="s">
+      <c r="F100" s="4" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="101" spans="1:6">
-      <c r="A101" t="s">
+    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75">
+      <c r="A101" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="B101">
+      <c r="B101" s="5">
         <v>643</v>
       </c>
-      <c r="C101">
+      <c r="C101" s="5">
         <v>260</v>
       </c>
-      <c r="D101">
+      <c r="D101" s="6">
         <v>7.52</v>
       </c>
-      <c r="E101" t="s">
+      <c r="E101" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="F101" t="s">
+      <c r="F101" s="4" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="102" spans="1:6">
-      <c r="A102" t="s">
+    <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="18.75">
+      <c r="A102" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="B102">
+      <c r="B102" s="5">
         <v>829</v>
       </c>
-      <c r="C102">
+      <c r="C102" s="5">
         <v>79</v>
       </c>
-      <c r="D102">
+      <c r="D102" s="6">
         <v>4.24</v>
       </c>
-      <c r="E102" t="s">
+      <c r="E102" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="F102" t="s">
+      <c r="F102" s="4" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="103" spans="1:6">
-      <c r="A103" t="s">
+    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="18.75">
+      <c r="A103" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="B103">
+      <c r="B103" s="5">
         <v>761</v>
       </c>
-      <c r="C103">
+      <c r="C103" s="5">
         <v>138</v>
       </c>
-      <c r="D103">
+      <c r="D103" s="6">
         <v>4.24</v>
       </c>
-      <c r="E103" t="s">
+      <c r="E103" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="F103" t="s">
+      <c r="F103" s="4" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
-      <c r="A104" t="s">
+    <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="18.75">
+      <c r="A104" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="B104">
+      <c r="B104" s="5">
         <v>648</v>
       </c>
-      <c r="C104">
+      <c r="C104" s="5">
         <v>247</v>
       </c>
-      <c r="D104">
+      <c r="D104" s="6">
         <v>4.13</v>
       </c>
-      <c r="E104" t="s">
+      <c r="E104" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="F104" t="s">
+      <c r="F104" s="4" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="105" spans="1:6">
-      <c r="A105" t="s">
+    <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="18.75">
+      <c r="A105" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="B105">
+      <c r="B105" s="5">
         <v>853</v>
       </c>
-      <c r="C105">
+      <c r="C105" s="5">
         <v>71</v>
       </c>
-      <c r="D105">
+      <c r="D105" s="6">
         <v>4.51</v>
       </c>
-      <c r="E105" t="s">
+      <c r="E105" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="F105" t="s">
+      <c r="F105" s="4" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="106" spans="1:6">
-      <c r="A106" t="s">
+    <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="18.75">
+      <c r="A106" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="B106">
+      <c r="B106" s="5">
         <v>733</v>
       </c>
-      <c r="C106">
+      <c r="C106" s="5">
         <v>168</v>
       </c>
-      <c r="D106">
+      <c r="D106" s="6">
         <v>4.11</v>
       </c>
-      <c r="E106" t="s">
+      <c r="E106" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="F106" t="s">
+      <c r="F106" s="4" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="107" spans="1:6">
-      <c r="A107" t="s">
+    <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="18.75">
+      <c r="A107" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="B107">
+      <c r="B107" s="5">
         <v>810</v>
       </c>
-      <c r="C107">
+      <c r="C107" s="5">
         <v>142</v>
       </c>
-      <c r="D107">
+      <c r="D107" s="6">
         <v>4.01</v>
       </c>
-      <c r="E107" t="s">
+      <c r="E107" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="F107" t="s">
+      <c r="F107" s="4" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="108" spans="1:6">
-      <c r="A108" t="s">
+    <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="18.75">
+      <c r="A108" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="B108">
+      <c r="B108" s="5">
         <v>680</v>
       </c>
-      <c r="C108">
+      <c r="C108" s="5">
         <v>241</v>
       </c>
-      <c r="D108">
+      <c r="D108" s="6">
         <v>4.76</v>
       </c>
-      <c r="E108" t="s">
+      <c r="E108" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="F108" t="s">
+      <c r="F108" s="4" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="109" spans="1:6">
-      <c r="A109" t="s">
+    <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="18.75">
+      <c r="A109" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="B109">
+      <c r="B109" s="5">
         <v>978</v>
       </c>
-      <c r="C109">
+      <c r="C109" s="5">
         <v>4</v>
       </c>
-      <c r="D109">
+      <c r="D109" s="6">
         <v>6.39</v>
       </c>
-      <c r="E109" t="s">
+      <c r="E109" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="F109" t="s">
+      <c r="F109" s="4" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="110" spans="1:6">
-      <c r="A110" t="s">
+    <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="18.75">
+      <c r="A110" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="B110">
+      <c r="B110" s="5">
         <v>788</v>
       </c>
-      <c r="C110">
+      <c r="C110" s="5">
         <v>155</v>
       </c>
-      <c r="D110">
+      <c r="D110" s="6">
         <v>4.07</v>
       </c>
-      <c r="E110" t="s">
+      <c r="E110" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="F110" t="s">
+      <c r="F110" s="4" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
-      <c r="A111" t="s">
+    <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="18.75">
+      <c r="A111" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="B111">
+      <c r="B111" s="5">
         <v>674</v>
       </c>
-      <c r="C111">
+      <c r="C111" s="5">
         <v>280</v>
       </c>
-      <c r="D111">
+      <c r="D111" s="6">
         <v>4.77</v>
       </c>
-      <c r="E111" t="s">
+      <c r="E111" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="F111" t="s">
+      <c r="F111" s="4" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
-      <c r="A112" t="s">
+    <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="18.75">
+      <c r="A112" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="B112">
+      <c r="B112" s="5">
         <v>976</v>
       </c>
-      <c r="C112">
+      <c r="C112" s="5">
         <v>31</v>
       </c>
-      <c r="D112">
+      <c r="D112" s="6">
         <v>4.39</v>
       </c>
-      <c r="E112" t="s">
+      <c r="E112" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="F112" t="s">
+      <c r="F112" s="4" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
-      <c r="A113" t="s">
+    <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="18.75">
+      <c r="A113" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="B113">
+      <c r="B113" s="5">
         <v>355</v>
       </c>
-      <c r="C113">
+      <c r="C113" s="5">
         <v>582</v>
       </c>
-      <c r="D113">
+      <c r="D113" s="6">
         <v>4.9</v>
       </c>
-      <c r="E113" t="s">
+      <c r="E113" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="F113" t="s">
+      <c r="F113" s="4" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
-      <c r="A114" t="s">
+    <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="18.75">
+      <c r="A114" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="B114">
+      <c r="B114" s="5">
         <v>978</v>
       </c>
-      <c r="C114">
+      <c r="C114" s="5">
         <v>31</v>
       </c>
-      <c r="D114">
+      <c r="D114" s="6">
         <v>5.86</v>
       </c>
-      <c r="E114" t="s">
+      <c r="E114" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="F114" t="s">
+      <c r="F114" s="4" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="115" spans="1:6">
-      <c r="A115" t="s">
+    <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="18.75">
+      <c r="A115" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="B115">
+      <c r="B115" s="5">
         <v>756</v>
       </c>
-      <c r="C115">
+      <c r="C115" s="5">
         <v>239</v>
       </c>
-      <c r="D115">
+      <c r="D115" s="6">
         <v>5.44</v>
       </c>
-      <c r="E115" t="s">
+      <c r="E115" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="F115" t="s">
+      <c r="F115" s="4" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
-      <c r="A116" t="s">
+    <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="18.75">
+      <c r="A116" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="B116">
+      <c r="B116" s="5">
         <v>962</v>
       </c>
-      <c r="C116">
+      <c r="C116" s="5">
         <v>45</v>
       </c>
-      <c r="D116">
+      <c r="D116" s="6">
         <v>5.23</v>
       </c>
-      <c r="E116" t="s">
+      <c r="E116" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="F116" t="s">
+      <c r="F116" s="4" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
-      <c r="A117" t="s">
+    <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="18.75">
+      <c r="A117" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="B117">
+      <c r="B117" s="5">
         <v>924</v>
       </c>
-      <c r="C117">
+      <c r="C117" s="5">
         <v>61</v>
       </c>
-      <c r="D117">
+      <c r="D117" s="6">
         <v>4.79</v>
       </c>
-      <c r="E117" t="s">
+      <c r="E117" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="F117" t="s">
+      <c r="F117" s="4" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
-      <c r="A118" t="s">
+    <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="18.75">
+      <c r="A118" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="B118">
+      <c r="B118" s="5">
         <v>513</v>
       </c>
-      <c r="C118">
+      <c r="C118" s="5">
         <v>462</v>
       </c>
-      <c r="D118">
+      <c r="D118" s="6">
         <v>4.39</v>
       </c>
-      <c r="E118" t="s">
+      <c r="E118" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="F118" t="s">
+      <c r="F118" s="4" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
-      <c r="A119" t="s">
+    <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="18.75">
+      <c r="A119" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="B119">
+      <c r="B119" s="5">
         <v>535</v>
       </c>
-      <c r="C119">
+      <c r="C119" s="5">
         <v>426</v>
       </c>
-      <c r="D119">
+      <c r="D119" s="6">
         <v>4.73</v>
       </c>
-      <c r="E119" t="s">
+      <c r="E119" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="F119" t="s">
+      <c r="F119" s="4" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
-      <c r="A120" t="s">
+    <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="18.75">
+      <c r="A120" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="B120">
+      <c r="B120" s="5">
         <v>838</v>
       </c>
-      <c r="C120">
+      <c r="C120" s="5">
         <v>135</v>
       </c>
-      <c r="D120">
+      <c r="D120" s="6">
         <v>5.06</v>
       </c>
-      <c r="E120" t="s">
+      <c r="E120" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="F120" t="s">
+      <c r="F120" s="4" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="121" spans="1:6">
-      <c r="A121" t="s">
+    <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="18.75">
+      <c r="A121" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="B121">
+      <c r="B121" s="5">
         <v>673</v>
       </c>
-      <c r="C121">
+      <c r="C121" s="5">
         <v>317</v>
       </c>
-      <c r="D121">
+      <c r="D121" s="6">
         <v>8.66</v>
       </c>
-      <c r="E121" t="s">
+      <c r="E121" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="F121" t="s">
+      <c r="F121" s="4" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
-      <c r="A122" t="s">
+    <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="18.75">
+      <c r="A122" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="B122">
+      <c r="B122" s="5">
         <v>256</v>
       </c>
-      <c r="C122">
+      <c r="C122" s="5">
         <v>763</v>
       </c>
-      <c r="D122">
+      <c r="D122" s="6">
         <v>4.18</v>
       </c>
-      <c r="E122" t="s">
+      <c r="E122" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="F122" t="s">
+      <c r="F122" s="4" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="123" spans="1:6">
-      <c r="A123" t="s">
+    <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="18.75">
+      <c r="A123" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="B123">
+      <c r="B123" s="5">
         <v>311</v>
       </c>
-      <c r="C123">
+      <c r="C123" s="5">
         <v>697</v>
       </c>
-      <c r="D123">
+      <c r="D123" s="6">
         <v>6.58</v>
       </c>
-      <c r="E123" t="s">
+      <c r="E123" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="F123" t="s">
+      <c r="F123" s="4" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="124" spans="1:6">
-      <c r="A124" t="s">
+    <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="18.75">
+      <c r="A124" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="B124">
+      <c r="B124" s="5">
         <v>652</v>
       </c>
-      <c r="C124">
+      <c r="C124" s="5">
         <v>360</v>
       </c>
-      <c r="D124">
+      <c r="D124" s="6">
         <v>5.86</v>
       </c>
-      <c r="E124" t="s">
+      <c r="E124" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="F124" t="s">
+      <c r="F124" s="4" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="125" spans="1:6">
-      <c r="A125" t="s">
+    <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="18.75">
+      <c r="A125" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="B125">
+      <c r="B125" s="5">
         <v>721</v>
       </c>
-      <c r="C125">
+      <c r="C125" s="5">
         <v>266</v>
       </c>
-      <c r="D125">
+      <c r="D125" s="6">
         <v>4.36</v>
       </c>
-      <c r="E125" t="s">
+      <c r="E125" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="F125" t="s">
+      <c r="F125" s="4" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
-      <c r="A126" t="s">
+    <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="18.75">
+      <c r="A126" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="B126">
+      <c r="B126" s="5">
         <v>819</v>
       </c>
-      <c r="C126">
+      <c r="C126" s="5">
         <v>186</v>
       </c>
-      <c r="D126">
+      <c r="D126" s="6">
         <v>7.28</v>
       </c>
-      <c r="E126" t="s">
+      <c r="E126" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="F126" t="s">
+      <c r="F126" s="4" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
-      <c r="A127" t="s">
+    <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="18.75">
+      <c r="A127" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="B127">
+      <c r="B127" s="5">
         <v>910</v>
       </c>
-      <c r="C127">
+      <c r="C127" s="5">
         <v>130</v>
       </c>
-      <c r="D127">
+      <c r="D127" s="6">
         <v>6.06</v>
       </c>
-      <c r="E127" t="s">
+      <c r="E127" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="F127" t="s">
+      <c r="F127" s="4" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
-      <c r="A128" t="s">
+    <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="18.75">
+      <c r="A128" s="4" t="s">
         <v>366</v>
       </c>
-      <c r="B128">
+      <c r="B128" s="5">
         <v>367</v>
       </c>
-      <c r="C128">
+      <c r="C128" s="5">
         <v>682</v>
       </c>
-      <c r="D128">
+      <c r="D128" s="6">
         <v>4.42</v>
       </c>
-      <c r="E128" t="s">
+      <c r="E128" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="F128" t="s">
+      <c r="F128" s="4" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="129" spans="1:6">
-      <c r="A129" t="s">
+    <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="18.75">
+      <c r="A129" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="B129">
+      <c r="B129" s="5">
         <v>529</v>
       </c>
-      <c r="C129">
+      <c r="C129" s="5">
         <v>513</v>
       </c>
-      <c r="D129">
+      <c r="D129" s="6">
         <v>4.5</v>
       </c>
-      <c r="E129" t="s">
+      <c r="E129" s="4" t="s">
         <v>370</v>
       </c>
-      <c r="F129" t="s">
+      <c r="F129" s="4" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
-      <c r="A130" t="s">
+    <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="18.75">
+      <c r="A130" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="B130">
+      <c r="B130" s="5">
         <v>564</v>
       </c>
-      <c r="C130">
+      <c r="C130" s="5">
         <v>478</v>
       </c>
-      <c r="D130">
+      <c r="D130" s="6">
         <v>4.68</v>
       </c>
-      <c r="E130" t="s">
+      <c r="E130" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="F130" t="s">
+      <c r="F130" s="4" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="131" spans="1:6">
-      <c r="A131" t="s">
+    <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="18.75">
+      <c r="A131" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="B131">
+      <c r="B131" s="5">
         <v>801</v>
       </c>
-      <c r="C131">
+      <c r="C131" s="5">
         <v>242</v>
       </c>
-      <c r="D131">
+      <c r="D131" s="6">
         <v>7.03</v>
       </c>
-      <c r="E131" t="s">
+      <c r="E131" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="F131" t="s">
+      <c r="F131" s="4" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
-      <c r="A132" t="s">
+    <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="18.75">
+      <c r="A132" s="4" t="s">
         <v>377</v>
       </c>
-      <c r="B132">
+      <c r="B132" s="5">
         <v>953</v>
       </c>
-      <c r="C132">
+      <c r="C132" s="5">
         <v>107</v>
       </c>
-      <c r="D132">
+      <c r="D132" s="6">
         <v>5.74</v>
       </c>
-      <c r="E132" t="s">
+      <c r="E132" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="F132" t="s">
+      <c r="F132" s="4" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="133" spans="1:6">
-      <c r="A133" t="s">
+    <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="18.75">
+      <c r="A133" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="B133">
+      <c r="B133" s="5">
         <v>958</v>
       </c>
-      <c r="C133">
+      <c r="C133" s="5">
         <v>99</v>
       </c>
-      <c r="D133">
+      <c r="D133" s="6">
         <v>8.42</v>
       </c>
-      <c r="E133" t="s">
+      <c r="E133" s="4" t="s">
         <v>377</v>
       </c>
-      <c r="F133" t="s">
+      <c r="F133" s="4" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="134" spans="1:6">
-      <c r="A134" t="s">
+    <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="18.75">
+      <c r="A134" s="4" t="s">
         <v>382</v>
       </c>
-      <c r="B134">
+      <c r="B134" s="5">
         <v>475</v>
       </c>
-      <c r="C134">
+      <c r="C134" s="5">
         <v>579</v>
       </c>
-      <c r="D134">
+      <c r="D134" s="6">
         <v>6.47</v>
       </c>
-      <c r="E134" t="s">
+      <c r="E134" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="F134" t="s">
+      <c r="F134" s="4" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="135" spans="1:6">
-      <c r="A135" t="s">
+    <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="18.75">
+      <c r="A135" s="4" t="s">
         <v>385</v>
       </c>
-      <c r="B135">
+      <c r="B135" s="5">
         <v>485</v>
       </c>
-      <c r="C135">
+      <c r="C135" s="5">
         <v>569</v>
       </c>
-      <c r="D135">
+      <c r="D135" s="6">
         <v>4.52</v>
       </c>
-      <c r="E135" t="s">
+      <c r="E135" s="4" t="s">
         <v>382</v>
       </c>
-      <c r="F135" t="s">
+      <c r="F135" s="4" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="136" spans="1:6">
-      <c r="A136" t="s">
+    <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="18.75">
+      <c r="A136" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="B136">
+      <c r="B136" s="5">
         <v>973</v>
       </c>
-      <c r="C136">
+      <c r="C136" s="5">
         <v>74</v>
       </c>
-      <c r="D136">
+      <c r="D136" s="6">
         <v>13.21</v>
       </c>
-      <c r="E136" t="s">
+      <c r="E136" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="F136" t="s">
+      <c r="F136" s="4" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="137" spans="1:6">
-      <c r="A137" t="s">
+    <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="18.75">
+      <c r="A137" s="4" t="s">
         <v>390</v>
       </c>
-      <c r="B137">
+      <c r="B137" s="5">
         <v>781</v>
       </c>
-      <c r="C137">
+      <c r="C137" s="5">
         <v>287</v>
       </c>
-      <c r="D137">
+      <c r="D137" s="6">
         <v>5.09</v>
       </c>
-      <c r="E137" t="s">
+      <c r="E137" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="F137" t="s">
+      <c r="F137" s="4" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="138" spans="1:6">
-      <c r="A138" t="s">
+    <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="18.75">
+      <c r="A138" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="B138">
+      <c r="B138" s="5">
         <v>598</v>
       </c>
-      <c r="C138">
+      <c r="C138" s="5">
         <v>481</v>
       </c>
-      <c r="D138">
+      <c r="D138" s="6">
         <v>7.27</v>
       </c>
-      <c r="E138" t="s">
+      <c r="E138" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="F138" t="s">
+      <c r="F138" s="4" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="139" spans="1:6">
-      <c r="A139" t="s">
+    <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="18.75">
+      <c r="A139" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="B139">
+      <c r="B139" s="5">
         <v>217</v>
       </c>
-      <c r="C139">
+      <c r="C139" s="5">
         <v>856</v>
       </c>
-      <c r="D139">
+      <c r="D139" s="6">
         <v>9.52</v>
       </c>
-      <c r="E139" t="s">
+      <c r="E139" s="4" t="s">
         <v>397</v>
       </c>
-      <c r="F139" t="s">
+      <c r="F139" s="4" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
-      <c r="A140" t="s">
+    <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="18.75">
+      <c r="A140" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="B140">
+      <c r="B140" s="5">
         <v>1035</v>
       </c>
-      <c r="C140">
+      <c r="C140" s="5">
         <v>37</v>
       </c>
-      <c r="D140">
+      <c r="D140" s="6">
         <v>7.69</v>
       </c>
-      <c r="E140" t="s">
+      <c r="E140" s="4" t="s">
         <v>400</v>
       </c>
-      <c r="F140" t="s">
+      <c r="F140" s="4" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
-      <c r="A141" t="s">
+    <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="18.75">
+      <c r="A141" s="4" t="s">
         <v>402</v>
       </c>
-      <c r="B141">
+      <c r="B141" s="5">
         <v>1034</v>
       </c>
-      <c r="C141">
+      <c r="C141" s="5">
         <v>48</v>
       </c>
-      <c r="D141">
+      <c r="D141" s="6">
         <v>8.24</v>
       </c>
-      <c r="E141" t="s">
+      <c r="E141" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="F141" t="s">
+      <c r="F141" s="4" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
-      <c r="A142" t="s">
+    <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="18.75">
+      <c r="A142" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="B142">
+      <c r="B142" s="5">
         <v>982</v>
       </c>
-      <c r="C142">
+      <c r="C142" s="5">
         <v>131</v>
       </c>
-      <c r="D142">
+      <c r="D142" s="6">
         <v>4.05</v>
       </c>
-      <c r="E142" t="s">
+      <c r="E142" s="4" t="s">
         <v>406</v>
       </c>
-      <c r="F142" t="s">
+      <c r="F142" s="4" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="143" spans="1:6">
-      <c r="A143" t="s">
+    <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="18.75">
+      <c r="A143" s="4" t="s">
         <v>408</v>
       </c>
-      <c r="B143">
+      <c r="B143" s="5">
         <v>475</v>
       </c>
-      <c r="C143">
+      <c r="C143" s="5">
         <v>669</v>
       </c>
-      <c r="D143">
+      <c r="D143" s="6">
         <v>4.25</v>
       </c>
-      <c r="E143" t="s">
+      <c r="E143" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="F143" t="s">
+      <c r="F143" s="4" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="144" spans="1:6">
-      <c r="A144" t="s">
+    <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="18.75">
+      <c r="A144" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="B144">
+      <c r="B144" s="5">
         <v>615</v>
       </c>
-      <c r="C144">
+      <c r="C144" s="5">
         <v>501</v>
       </c>
-      <c r="D144">
+      <c r="D144" s="6">
         <v>6.39</v>
       </c>
-      <c r="E144" t="s">
+      <c r="E144" s="4" t="s">
         <v>412</v>
       </c>
-      <c r="F144" t="s">
+      <c r="F144" s="4" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
-      <c r="A145" t="s">
+    <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="18.75">
+      <c r="A145" s="4" t="s">
         <v>414</v>
       </c>
-      <c r="B145">
+      <c r="B145" s="5">
         <v>1123</v>
       </c>
-      <c r="C145">
+      <c r="C145" s="5">
         <v>47</v>
       </c>
-      <c r="D145">
+      <c r="D145" s="6">
         <v>5.17</v>
       </c>
-      <c r="E145" t="s">
+      <c r="E145" s="4" t="s">
         <v>415</v>
       </c>
-      <c r="F145" t="s">
+      <c r="F145" s="4" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="146" spans="1:6">
-      <c r="A146" t="s">
+    <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="18.75">
+      <c r="A146" s="4" t="s">
         <v>417</v>
       </c>
-      <c r="B146">
+      <c r="B146" s="5">
         <v>1291</v>
       </c>
-      <c r="C146">
+      <c r="C146" s="5">
         <v>51</v>
       </c>
-      <c r="D146">
+      <c r="D146" s="6">
         <v>4.08</v>
       </c>
-      <c r="E146" t="s">
+      <c r="E146" s="4" t="s">
         <v>418</v>
       </c>
-      <c r="F146" t="s">
+      <c r="F146" s="4" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="147" spans="1:6">
-      <c r="A147" t="s">
+    <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="18.75">
+      <c r="A147" s="4" t="s">
         <v>420</v>
       </c>
-      <c r="B147">
+      <c r="B147" s="5">
         <v>1286</v>
       </c>
-      <c r="C147">
+      <c r="C147" s="5">
         <v>119</v>
       </c>
-      <c r="D147">
+      <c r="D147" s="6">
         <v>4.8</v>
       </c>
-      <c r="E147" t="s">
+      <c r="E147" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="F147" t="s">
+      <c r="F147" s="4" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="148" spans="1:6">
-      <c r="A148" t="s">
+    <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="18.75">
+      <c r="A148" s="4" t="s">
         <v>423</v>
       </c>
-      <c r="B148">
+      <c r="B148" s="5">
         <v>255</v>
       </c>
-      <c r="C148">
+      <c r="C148" s="5">
         <v>1187</v>
       </c>
-      <c r="D148">
+      <c r="D148" s="6">
         <v>4.36</v>
       </c>
-      <c r="E148" t="s">
+      <c r="E148" s="4" t="s">
         <v>424</v>
       </c>
-      <c r="F148" t="s">
+      <c r="F148" s="4" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="149" spans="1:6">
-      <c r="A149" t="s">
+    <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="18.75">
+      <c r="A149" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="B149">
+      <c r="B149" s="5">
         <v>1431</v>
       </c>
-      <c r="C149">
+      <c r="C149" s="5">
         <v>39</v>
       </c>
-      <c r="D149">
+      <c r="D149" s="6">
         <v>4.22</v>
       </c>
-      <c r="E149" t="s">
+      <c r="E149" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="F149" t="s">
+      <c r="F149" s="4" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="150" spans="1:6">
-      <c r="A150" t="s">
+    <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="18.75">
+      <c r="A150" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="B150">
+      <c r="B150" s="5">
         <v>1498</v>
       </c>
-      <c r="C150">
+      <c r="C150" s="5">
         <v>2</v>
       </c>
-      <c r="D150">
+      <c r="D150" s="6">
         <v>7.25</v>
       </c>
-      <c r="E150" t="s">
+      <c r="E150" s="4" t="s">
         <v>429</v>
       </c>
-      <c r="F150" t="s">
+      <c r="F150" s="4" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="151" spans="1:6">
-      <c r="A151" t="s">
+    <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="18.75">
+      <c r="A151" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="B151">
+      <c r="B151" s="5">
         <v>722</v>
       </c>
-      <c r="C151">
+      <c r="C151" s="5">
         <v>731</v>
       </c>
-      <c r="D151">
+      <c r="D151" s="6">
         <v>6.07</v>
       </c>
-      <c r="E151" t="s">
+      <c r="E151" s="4" t="s">
         <v>432</v>
       </c>
-      <c r="F151" t="s">
+      <c r="F151" s="4" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
-      <c r="A152" t="s">
+    <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="18.75">
+      <c r="A152" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="B152">
+      <c r="B152" s="5">
         <v>1448</v>
       </c>
-      <c r="C152">
+      <c r="C152" s="5">
         <v>137</v>
       </c>
-      <c r="D152">
+      <c r="D152" s="6">
         <v>4.37</v>
       </c>
-      <c r="E152" t="s">
+      <c r="E152" s="4" t="s">
         <v>435</v>
       </c>
-      <c r="F152" t="s">
+      <c r="F152" s="4" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="153" spans="1:6">
-      <c r="A153" t="s">
+    <row x14ac:dyDescent="0.25" r="153" customHeight="1" ht="18.75">
+      <c r="A153" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="B153">
+      <c r="B153" s="5">
         <v>1116</v>
       </c>
-      <c r="C153">
+      <c r="C153" s="5">
         <v>461</v>
       </c>
-      <c r="D153">
+      <c r="D153" s="6">
         <v>4.56</v>
       </c>
-      <c r="E153" t="s">
+      <c r="E153" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="F153" t="s">
+      <c r="F153" s="4" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
-      <c r="A154" t="s">
+    <row x14ac:dyDescent="0.25" r="154" customHeight="1" ht="18.75">
+      <c r="A154" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="B154">
+      <c r="B154" s="5">
         <v>1577</v>
       </c>
-      <c r="C154">
+      <c r="C154" s="5">
         <v>92</v>
       </c>
-      <c r="D154">
+      <c r="D154" s="6">
         <v>10.14</v>
       </c>
-      <c r="E154" t="s">
+      <c r="E154" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="F154" t="s">
+      <c r="F154" s="4" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="155" spans="1:6">
-      <c r="A155" t="s">
+    <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="18.75">
+      <c r="A155" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="B155">
+      <c r="B155" s="5">
         <v>659</v>
       </c>
-      <c r="C155">
+      <c r="C155" s="5">
         <v>1056</v>
       </c>
-      <c r="D155">
+      <c r="D155" s="6">
         <v>4.4</v>
       </c>
-      <c r="E155" t="s">
+      <c r="E155" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="F155" t="s">
+      <c r="F155" s="4" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="156" spans="1:6">
-      <c r="A156" t="s">
+    <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="18.75">
+      <c r="A156" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="B156">
+      <c r="B156" s="5">
         <v>1136</v>
       </c>
-      <c r="C156">
+      <c r="C156" s="5">
         <v>637</v>
       </c>
-      <c r="D156">
+      <c r="D156" s="6">
         <v>4.54</v>
       </c>
-      <c r="E156" t="s">
+      <c r="E156" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="F156" t="s">
+      <c r="F156" s="4" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="157" spans="1:6">
-      <c r="A157" t="s">
+    <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="18.75">
+      <c r="A157" s="4" t="s">
         <v>449</v>
       </c>
-      <c r="B157">
+      <c r="B157" s="5">
         <v>1548</v>
       </c>
-      <c r="C157">
+      <c r="C157" s="5">
         <v>527</v>
       </c>
-      <c r="D157">
+      <c r="D157" s="6">
         <v>6.11</v>
       </c>
-      <c r="E157" t="s">
+      <c r="E157" s="4" t="s">
         <v>450</v>
       </c>
-      <c r="F157" t="s">
+      <c r="F157" s="4" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="158" spans="1:6">
-      <c r="A158" t="s">
+    <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="18.75">
+      <c r="A158" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="B158">
+      <c r="B158" s="5">
         <v>1957</v>
       </c>
-      <c r="C158">
+      <c r="C158" s="5">
         <v>145</v>
       </c>
-      <c r="D158">
+      <c r="D158" s="6">
         <v>5.57</v>
       </c>
-      <c r="E158" t="s">
+      <c r="E158" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="F158" t="s">
+      <c r="F158" s="4" t="s">
         <v>454</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:F160">
-    <sortCondition ref="A143"/>
-  </sortState>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>